--- a/LineClass/level_interchange.xlsx
+++ b/LineClass/level_interchange.xlsx
@@ -609,7 +609,7 @@
         <v>93.521</v>
       </c>
       <c r="H2" t="n">
-        <v>104.2</v>
+        <v>104.1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
         <v>117478.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P2" t="n">
         <v>1.36</v>
@@ -656,31 +656,31 @@
         <v>13</v>
       </c>
       <c r="U2" t="n">
-        <v>-5.1</v>
+        <v>-19.72</v>
       </c>
       <c r="V2" t="n">
-        <v>-12.24</v>
+        <v>-11.22</v>
       </c>
       <c r="W2" t="n">
-        <v>0.549</v>
+        <v>0.46</v>
       </c>
       <c r="X2" t="n">
-        <v>0.599</v>
+        <v>0.923</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.339</v>
+        <v>0.543</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.535</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.366</v>
+        <v>2.104</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.831</v>
+        <v>0.911</v>
       </c>
       <c r="AC2" t="n">
-        <v>-17.34</v>
+        <v>-30.93</v>
       </c>
       <c r="AD2" t="n">
         <v>0.0025</v>
@@ -770,16 +770,16 @@
         <v>10</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.68</v>
+        <v>-0.87</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.86</v>
+        <v>-3.18</v>
       </c>
       <c r="W3" t="n">
-        <v>0.487</v>
+        <v>0.478</v>
       </c>
       <c r="X3" t="n">
-        <v>0.605</v>
+        <v>0.615</v>
       </c>
       <c r="Y3" t="n">
         <v>0.301</v>
@@ -788,16 +788,16 @@
         <v>0.343</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.622</v>
+        <v>1.626</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.38</v>
+        <v>1.377</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.53</v>
+        <v>-4.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0076</v>
+        <v>0.0152</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -809,109 +809,109 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>059003.000593</t>
+          <t>059003.000402</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>059003.000596</t>
+          <t>059003.000485</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11/2</t>
+          <t>3/2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>o</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>136555.5261</v>
+        <v>118201.5226</v>
       </c>
       <c r="F4" t="n">
-        <v>136570.8444</v>
+        <v>118224.0821</v>
       </c>
       <c r="G4" t="n">
-        <v>15.318</v>
+        <v>22.559</v>
       </c>
       <c r="H4" t="n">
-        <v>22.2</v>
+        <v>104.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>f25g</t>
+          <t>f25f</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>_3H4I</t>
+          <t>~3F4F</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>f25g</t>
+          <t>f25f</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>_3H4H</t>
+          <t>~3F4F</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>136525.2</v>
+        <v>118111.3</v>
       </c>
       <c r="N4" t="n">
-        <v>136553.9</v>
+        <v>118035</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>1.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U4" t="n">
-        <v>0.96</v>
+        <v>-5.6</v>
       </c>
       <c r="V4" t="n">
-        <v>4.98</v>
+        <v>4.65</v>
       </c>
       <c r="W4" t="n">
-        <v>0.797</v>
+        <v>0.633</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.154</v>
+        <v>0.91</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.629</v>
+        <v>0.373</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.067</v>
+        <v>0.212</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.579</v>
+        <v>1.752</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.553</v>
+        <v>1.707</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.94</v>
+        <v>-0.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0178</v>
+        <v>0.0203</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -923,17 +923,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>059003.000607</t>
+          <t>059003.000593</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>059003.000611</t>
+          <t>059003.000596</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13/2</t>
+          <t>11/2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>138788.5991</v>
+        <v>136555.5261</v>
       </c>
       <c r="F5" t="n">
-        <v>138799.4366</v>
+        <v>136570.8444</v>
       </c>
       <c r="G5" t="n">
-        <v>10.837</v>
+        <v>15.318</v>
       </c>
       <c r="H5" t="n">
         <v>22.2</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>_3H2I</t>
+          <t>_3H4I</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>138763.4</v>
+        <v>136525.2</v>
       </c>
       <c r="N5" t="n">
-        <v>138784.9</v>
+        <v>136553.9</v>
       </c>
       <c r="O5" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -992,40 +992,40 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U5" t="n">
-        <v>9.06</v>
+        <v>1.07</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>5.54</v>
       </c>
       <c r="W5" t="n">
-        <v>0.595</v>
+        <v>0.741</v>
       </c>
       <c r="X5" t="n">
-        <v>0.202</v>
+        <v>0.004</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.421</v>
+        <v>0.629</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.406</v>
+        <v>-0.067</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.748</v>
+        <v>0.655</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.02</v>
+        <v>1.583</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.06</v>
+        <v>6.61</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.033</v>
+        <v>0.043</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
@@ -1037,17 +1037,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>059003.000402</t>
+          <t>059003.000513</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>059003.000485</t>
+          <t>059003.000514</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3/2</t>
+          <t>11/2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1056,16 +1056,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>118201.5226</v>
+        <v>134008.0887</v>
       </c>
       <c r="F6" t="n">
-        <v>118224.0821</v>
+        <v>134069.3997</v>
       </c>
       <c r="G6" t="n">
-        <v>22.559</v>
+        <v>61.311</v>
       </c>
       <c r="H6" t="n">
-        <v>104.2</v>
+        <v>104.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1074,72 +1074,72 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>~3F4F</t>
+          <t>~3P4G</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>f25f</t>
+          <t>f26f</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>~3F4F</t>
+          <t>~3H2I</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>118111.3</v>
+        <v>134293.1</v>
       </c>
       <c r="N6" t="n">
-        <v>118035</v>
+        <v>134090.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.6</v>
+        <v>-1.82</v>
       </c>
       <c r="P6" t="n">
-        <v>1.08</v>
+        <v>-2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U6" t="n">
-        <v>9.289999999999999</v>
+        <v>-2.08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.23</v>
+        <v>8.92</v>
       </c>
       <c r="W6" t="n">
-        <v>0.625</v>
+        <v>0.396</v>
       </c>
       <c r="X6" t="n">
-        <v>0.172</v>
+        <v>1.343</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.21</v>
+        <v>1.269</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.192</v>
+        <v>0.474</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.818</v>
+        <v>1.519</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.369</v>
+        <v>2.066</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.52</v>
+        <v>6.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0406</v>
+        <v>0.043</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1151,67 +1151,67 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>059003.000513</t>
+          <t>059003.000607</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>059003.000514</t>
+          <t>059003.000611</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11/2</t>
+          <t>13/2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>134008.0887</v>
+        <v>138788.5991</v>
       </c>
       <c r="F7" t="n">
-        <v>134069.3997</v>
+        <v>138799.4366</v>
       </c>
       <c r="G7" t="n">
-        <v>61.311</v>
+        <v>10.837</v>
       </c>
       <c r="H7" t="n">
-        <v>104.2</v>
+        <v>22.2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>f25f</t>
+          <t>f25g</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>~3P4G</t>
+          <t>_3H2I</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>f26f</t>
+          <t>f25g</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>~3H2I</t>
+          <t>_3H4H</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>134293.1</v>
+        <v>138763.4</v>
       </c>
       <c r="N7" t="n">
-        <v>134090.8</v>
+        <v>138784.9</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.82</v>
+        <v>0.17</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.15</v>
+        <v>1.62</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1220,40 +1220,40 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>3.1</v>
+        <v>10.09</v>
       </c>
       <c r="V7" t="n">
-        <v>10.56</v>
+        <v>1.12</v>
       </c>
       <c r="W7" t="n">
-        <v>0.337</v>
+        <v>0.595</v>
       </c>
       <c r="X7" t="n">
-        <v>0.245</v>
+        <v>0.202</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.257</v>
+        <v>0.421</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.207</v>
+        <v>-0.406</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.593</v>
+        <v>0.748</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.702</v>
+        <v>2.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>13.66</v>
+        <v>11.21</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0482</v>
+        <v>0.0684</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1265,109 +1265,109 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>059003.000608</t>
+          <t>059003.000394</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>059003.000609</t>
+          <t>059003.000480</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15/2</t>
+          <t>11/2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>o</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>138787.9547</v>
+        <v>117322.9754</v>
       </c>
       <c r="F8" t="n">
-        <v>138794.6045</v>
+        <v>117385.0768</v>
       </c>
       <c r="G8" t="n">
-        <v>6.65</v>
+        <v>62.101</v>
       </c>
       <c r="H8" t="n">
-        <v>22.2</v>
+        <v>104.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>f25g</t>
+          <t>f25f</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>_3H4I</t>
+          <t>~3F4I</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>f25g</t>
+          <t>f27p</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>_3H2K</t>
+          <t>~3H4G</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>138761.2</v>
+        <v>117294.7</v>
       </c>
       <c r="N8" t="n">
-        <v>138766</v>
+        <v>117386.8</v>
       </c>
       <c r="O8" t="n">
-        <v>0.99</v>
+        <v>-1.98</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5</v>
+        <v>0.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="U8" t="n">
-        <v>17.01</v>
+        <v>4.56</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>1.037</v>
+        <v>0.95</v>
       </c>
       <c r="X8" t="n">
-        <v>0.081</v>
+        <v>1.032</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.759</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.783</v>
+        <v>0.489</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.709</v>
+        <v>0.901</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.674</v>
+        <v>1.603</v>
       </c>
       <c r="AC8" t="n">
-        <v>17.11</v>
+        <v>13.51</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0584</v>
+        <v>0.0861</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1379,109 +1379,109 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>059003.000225</t>
+          <t>059003.000608</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>059003.000226</t>
+          <t>059003.000609</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13/2</t>
+          <t>15/2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65967.11840000001</v>
+        <v>138787.9547</v>
       </c>
       <c r="F9" t="n">
-        <v>66148.3511</v>
+        <v>138794.6045</v>
       </c>
       <c r="G9" t="n">
-        <v>181.233</v>
+        <v>6.65</v>
       </c>
       <c r="H9" t="n">
-        <v>207.6</v>
+        <v>22.2</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>f5d2</t>
+          <t>f25g</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>~3F4I</t>
+          <t>_3H4I</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>f5d2</t>
+          <t>f25g</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>~3F4H</t>
+          <t>_3H2K</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>65964.3</v>
+        <v>138761.2</v>
       </c>
       <c r="N9" t="n">
-        <v>66035.5</v>
+        <v>138766</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.33</v>
+        <v>0.99</v>
       </c>
       <c r="P9" t="n">
-        <v>0.89</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>21.58</v>
+        <v>18.95</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.46</v>
+        <v>0.11</v>
       </c>
       <c r="W9" t="n">
-        <v>0.725</v>
+        <v>1.037</v>
       </c>
       <c r="X9" t="n">
-        <v>0.344</v>
+        <v>0.081</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.483</v>
+        <v>0.759</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.456</v>
+        <v>0.783</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.703</v>
+        <v>0.709</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.072</v>
+        <v>2.674</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.12</v>
+        <v>19.06</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0711</v>
+        <v>0.1114</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1493,109 +1493,109 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>059003.000419</t>
+          <t>059003.000225</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>059003.000572</t>
+          <t>059003.000226</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9/2</t>
+          <t>13/2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>o</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>129105.9341</v>
+        <v>65967.11840000001</v>
       </c>
       <c r="F10" t="n">
-        <v>129454.5059</v>
+        <v>66148.3511</v>
       </c>
       <c r="G10" t="n">
-        <v>348.572</v>
+        <v>181.233</v>
       </c>
       <c r="H10" t="n">
-        <v>404.2</v>
+        <v>207.6</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>f28s</t>
+          <t>f5d2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>_3H2H</t>
+          <t>~3F4I</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fd6p</t>
+          <t>f5d2</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>_1F2G</t>
+          <t>~3F4H</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>129091.1</v>
+        <v>65964.3</v>
       </c>
       <c r="N10" t="n">
-        <v>129387</v>
+        <v>66035.5</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7</v>
+        <v>-0.33</v>
       </c>
       <c r="P10" t="n">
-        <v>4.88</v>
+        <v>0.89</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="T10" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="U10" t="n">
-        <v>23.14</v>
+        <v>23.99</v>
       </c>
       <c r="V10" t="n">
-        <v>1.45</v>
+        <v>-2.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.343</v>
+        <v>0.723</v>
       </c>
       <c r="X10" t="n">
-        <v>0.491</v>
+        <v>0.334</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.822</v>
+        <v>0.494</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.365</v>
+        <v>0.468</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.066</v>
+        <v>1.723</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.881</v>
+        <v>2.095</v>
       </c>
       <c r="AC10" t="n">
-        <v>24.59</v>
+        <v>21.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1041</v>
+        <v>0.1215</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1635,7 +1635,7 @@
         <v>81.60899999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>104.2</v>
+        <v>104.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1647,13 +1647,25 @@
           <t>~3P4G</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>f25f</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>~3P4D</t>
+        </is>
+      </c>
       <c r="M11" t="n">
         <v>132831.9</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>133050.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-1.67</v>
+      </c>
       <c r="P11" t="n">
         <v>1.21</v>
       </c>
@@ -1670,34 +1682,34 @@
         <v>7</v>
       </c>
       <c r="U11" t="n">
-        <v>18.12</v>
+        <v>18.62</v>
       </c>
       <c r="V11" t="n">
-        <v>14.15</v>
+        <v>5.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.415</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>0.025</v>
+        <v>-0.038</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.821</v>
+        <v>2.298</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.269</v>
+        <v>0.466</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.03</v>
+        <v>0.857</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.93</v>
+        <v>2.415</v>
       </c>
       <c r="AC11" t="n">
-        <v>32.28</v>
+        <v>24.36</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.1421</v>
+        <v>0.1544</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1709,67 +1721,67 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>059003.000394</t>
+          <t>059003.000419</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>059003.000480</t>
+          <t>059003.000572</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11/2</t>
+          <t>9/2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>117322.9754</v>
+        <v>129105.9341</v>
       </c>
       <c r="F12" t="n">
-        <v>117385.0768</v>
+        <v>129454.5059</v>
       </c>
       <c r="G12" t="n">
-        <v>62.101</v>
+        <v>348.572</v>
       </c>
       <c r="H12" t="n">
-        <v>104.2</v>
+        <v>404.2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>f25f</t>
+          <t>f28s</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>~3F4I</t>
+          <t>_3H2H</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>f27p</t>
+          <t>fd6p</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>~3H4G</t>
+          <t>_1F2G</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>117294.7</v>
+        <v>129091.1</v>
       </c>
       <c r="N12" t="n">
-        <v>117386.8</v>
+        <v>129387</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.98</v>
+        <v>-0.7</v>
       </c>
       <c r="P12" t="n">
-        <v>0.87</v>
+        <v>4.88</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1778,40 +1790,40 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="U12" t="n">
-        <v>26.81</v>
+        <v>25.78</v>
       </c>
       <c r="V12" t="n">
-        <v>8.880000000000001</v>
+        <v>1.62</v>
       </c>
       <c r="W12" t="n">
-        <v>0.487</v>
+        <v>1.343</v>
       </c>
       <c r="X12" t="n">
-        <v>0.19</v>
+        <v>0.491</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.822</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.486</v>
+        <v>0.365</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.374</v>
+        <v>1.066</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.661</v>
+        <v>2.881</v>
       </c>
       <c r="AC12" t="n">
-        <v>35.68</v>
+        <v>27.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1751</v>
+        <v>0.1722</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1823,109 +1835,109 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>059003.000572</t>
+          <t>059003.000243</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>059003.000573</t>
+          <t>059003.000245</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9/2</t>
+          <t>7/2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>o</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>129454.5059</v>
+        <v>68331.73480000001</v>
       </c>
       <c r="F13" t="n">
-        <v>129744.1095</v>
+        <v>68492.4308</v>
       </c>
       <c r="G13" t="n">
-        <v>289.604</v>
+        <v>160.696</v>
       </c>
       <c r="H13" t="n">
-        <v>404.2</v>
+        <v>207.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>fd6p</t>
+          <t>f5d2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>_1F2G</t>
+          <t>~3F4F</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>f27d</t>
+          <t>f26p</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>_3H2H</t>
+          <t>~3F4F</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>129387</v>
+        <v>68461</v>
       </c>
       <c r="N13" t="n">
-        <v>129841.8</v>
+        <v>68298.39999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.41</v>
+        <v>0.29</v>
       </c>
       <c r="P13" t="n">
-        <v>0.88</v>
+        <v>0.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="T13" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="U13" t="n">
-        <v>17.99</v>
+        <v>-0.04</v>
       </c>
       <c r="V13" t="n">
-        <v>19.28</v>
+        <v>30.45</v>
       </c>
       <c r="W13" t="n">
-        <v>0.822</v>
+        <v>0.648</v>
       </c>
       <c r="X13" t="n">
-        <v>0.235</v>
+        <v>0.72</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.155</v>
+        <v>0.51</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.131</v>
+        <v>0.43</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.248</v>
+        <v>1.891</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.82</v>
+        <v>2.231</v>
       </c>
       <c r="AC13" t="n">
-        <v>37.28</v>
+        <v>30.41</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.1802</v>
+        <v>0.1924</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -1937,109 +1949,109 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>059003.000274</t>
+          <t>059003.000572</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>059003.000275</t>
+          <t>059003.000573</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5/2</t>
+          <t>9/2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>75560.72010000001</v>
+        <v>129454.5059</v>
       </c>
       <c r="F14" t="n">
-        <v>75614.7913</v>
+        <v>129744.1095</v>
       </c>
       <c r="G14" t="n">
-        <v>54.071</v>
+        <v>289.604</v>
       </c>
       <c r="H14" t="n">
-        <v>207.6</v>
+        <v>404.2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>f5d2</t>
+          <t>fd6p</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>~3F2D</t>
+          <t>_1F2G</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>f26p</t>
+          <t>f27d</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>~1D2F</t>
+          <t>_3H2H</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>75409.60000000001</v>
+        <v>129387</v>
       </c>
       <c r="N14" t="n">
-        <v>75694.5</v>
+        <v>129841.8</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.17</v>
+        <v>-4.41</v>
       </c>
       <c r="P14" t="n">
-        <v>0.99</v>
+        <v>0.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="U14" t="n">
-        <v>32</v>
+        <v>20.05</v>
       </c>
       <c r="V14" t="n">
-        <v>32.26</v>
+        <v>21.48</v>
       </c>
       <c r="W14" t="n">
-        <v>0.421</v>
+        <v>0.822</v>
       </c>
       <c r="X14" t="n">
-        <v>0.13</v>
+        <v>0.235</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.491</v>
+        <v>0.155</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.035</v>
+        <v>0.131</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.571</v>
+        <v>1.248</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.982</v>
+        <v>3.82</v>
       </c>
       <c r="AC14" t="n">
-        <v>64.26000000000001</v>
+        <v>41.53</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.3731</v>
+        <v>0.2759</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2051,67 +2063,67 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>059003.000243</t>
+          <t>059003.000101</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>059003.000245</t>
+          <t>059003.000102</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7/2</t>
+          <t>3/2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>68331.73480000001</v>
+        <v>24250.6158</v>
       </c>
       <c r="F15" t="n">
-        <v>68492.4308</v>
+        <v>24309.198</v>
       </c>
       <c r="G15" t="n">
-        <v>160.696</v>
+        <v>58.582</v>
       </c>
       <c r="H15" t="n">
-        <v>207.6</v>
+        <v>147.8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>f5d2</t>
+          <t>f25d</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>~3F4F</t>
+          <t>_3F4F</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>f26p</t>
+          <t>f25d</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>~3F4F</t>
+          <t>_3F2P</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>68461</v>
+        <v>24359.9</v>
       </c>
       <c r="N15" t="n">
-        <v>68298.39999999999</v>
+        <v>24565.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0.29</v>
+        <v>-2.13</v>
       </c>
       <c r="P15" t="n">
-        <v>0.15</v>
+        <v>-0.34</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2120,40 +2132,40 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="T15" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="U15" t="n">
-        <v>38.48</v>
+        <v>42.93</v>
       </c>
       <c r="V15" t="n">
-        <v>34.4</v>
+        <v>1.27</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.599</v>
       </c>
       <c r="X15" t="n">
-        <v>0.255</v>
+        <v>0.394</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.518</v>
+        <v>0.478</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.386</v>
+        <v>0.944</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.12</v>
+        <v>1.518</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.871</v>
+        <v>2.279</v>
       </c>
       <c r="AC15" t="n">
-        <v>72.88</v>
+        <v>44.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.4365</v>
+        <v>0.2987</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2165,17 +2177,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>059003.000380</t>
+          <t>059003.000274</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>059003.000472</t>
+          <t>059003.000275</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7/2</t>
+          <t>5/2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2184,90 +2196,90 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>115420.8987</v>
+        <v>75560.72010000001</v>
       </c>
       <c r="F16" t="n">
-        <v>115489.8006</v>
+        <v>75614.7913</v>
       </c>
       <c r="G16" t="n">
-        <v>68.902</v>
+        <v>54.071</v>
       </c>
       <c r="H16" t="n">
-        <v>104.2</v>
+        <v>207.6</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>f25f</t>
+          <t>f5d2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>~3H4D</t>
+          <t>~3F2D</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>f27p</t>
+          <t>f26p</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>~3H4G</t>
+          <t>~1D2F</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>115325.2</v>
+        <v>75409.60000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>115485.7</v>
+        <v>75694.5</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.01</v>
+        <v>-1.17</v>
       </c>
       <c r="P16" t="n">
-        <v>1.58</v>
+        <v>0.99</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="T16" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="U16" t="n">
-        <v>74.25</v>
+        <v>32.58</v>
       </c>
       <c r="V16" t="n">
-        <v>11.7</v>
+        <v>25.32</v>
       </c>
       <c r="W16" t="n">
-        <v>0.576</v>
+        <v>0.407</v>
       </c>
       <c r="X16" t="n">
-        <v>0.157</v>
+        <v>0.152</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.2</v>
+        <v>0.594</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.311</v>
+        <v>0.429</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.701</v>
+        <v>1.499</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.515</v>
+        <v>2.728</v>
       </c>
       <c r="AC16" t="n">
-        <v>85.95</v>
+        <v>57.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.5203</v>
+        <v>0.4051</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2279,17 +2291,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>059003.000244</t>
+          <t>059003.000380</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>059003.000247</t>
+          <t>059003.000472</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9/2</t>
+          <t>7/2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2298,90 +2310,90 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>68374.54059999999</v>
+        <v>115420.8987</v>
       </c>
       <c r="F17" t="n">
-        <v>68544.16740000001</v>
+        <v>115489.8006</v>
       </c>
       <c r="G17" t="n">
-        <v>169.627</v>
+        <v>68.902</v>
       </c>
       <c r="H17" t="n">
-        <v>207.6</v>
+        <v>104.1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>f26p</t>
+          <t>f25f</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>~1G2H</t>
+          <t>~3H4D</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>f5d2</t>
+          <t>f27p</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>~3F4G</t>
+          <t>~3H4G</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>68467.10000000001</v>
+        <v>115325.2</v>
       </c>
       <c r="N17" t="n">
-        <v>68706.7</v>
+        <v>115485.7</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6</v>
+        <v>-2.01</v>
       </c>
       <c r="P17" t="n">
-        <v>0.67</v>
+        <v>1.58</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="T17" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="U17" t="n">
-        <v>83.86</v>
+        <v>61.47</v>
       </c>
       <c r="V17" t="n">
-        <v>23.82</v>
+        <v>12.14</v>
       </c>
       <c r="W17" t="n">
-        <v>0.835</v>
+        <v>0.665</v>
       </c>
       <c r="X17" t="n">
-        <v>0.27</v>
+        <v>0.267</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.613</v>
+        <v>0.175</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.311</v>
+        <v>0.267</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.431</v>
+        <v>1.661</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.833</v>
+        <v>3.178</v>
       </c>
       <c r="AC17" t="n">
-        <v>107.68</v>
+        <v>73.61</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.6218</v>
+        <v>0.5266</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
@@ -2393,67 +2405,67 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>059003.000101</t>
+          <t>059003.000244</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>059003.000102</t>
+          <t>059003.000247</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3/2</t>
+          <t>9/2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>o</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>24250.6158</v>
+        <v>68374.54059999999</v>
       </c>
       <c r="F18" t="n">
-        <v>24309.198</v>
+        <v>68544.16740000001</v>
       </c>
       <c r="G18" t="n">
-        <v>58.582</v>
+        <v>169.627</v>
       </c>
       <c r="H18" t="n">
-        <v>147.8</v>
+        <v>207.6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>f25d</t>
+          <t>f26p</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>_3F4F</t>
+          <t>~1G2H</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>f25d</t>
+          <t>f5d2</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>_3F2P</t>
+          <t>~3F4G</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>24359.9</v>
+        <v>68467.10000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>24565.8</v>
+        <v>68706.7</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.13</v>
+        <v>-1.6</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.34</v>
+        <v>0.67</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2462,40 +2474,40 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="T18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="U18" t="n">
-        <v>62.58</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>57.11</v>
+        <v>16.15</v>
       </c>
       <c r="W18" t="n">
-        <v>0.508</v>
+        <v>0.803</v>
       </c>
       <c r="X18" t="n">
-        <v>0.141</v>
+        <v>0.231</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.462</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.152</v>
+        <v>0.503</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.615</v>
+        <v>1.296</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.366</v>
+        <v>2.629</v>
       </c>
       <c r="AC18" t="n">
-        <v>119.68</v>
+        <v>104.97</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.6624</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2582,34 +2594,34 @@
         <v>33</v>
       </c>
       <c r="U19" t="n">
-        <v>144.61</v>
+        <v>134.46</v>
       </c>
       <c r="V19" t="n">
-        <v>58.81</v>
+        <v>62.22</v>
       </c>
       <c r="W19" t="n">
-        <v>0.646</v>
+        <v>0.655</v>
       </c>
       <c r="X19" t="n">
-        <v>0.317</v>
+        <v>0.441</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.239</v>
+        <v>0.267</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.139</v>
+        <v>0.196</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.724</v>
+        <v>1.709</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.645</v>
+        <v>3.445</v>
       </c>
       <c r="AC19" t="n">
-        <v>203.42</v>
+        <v>196.67</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.8934</v>
+        <v>0.919</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
